--- a/corpus/templates/nested-groups/template.xlsx
+++ b/corpus/templates/nested-groups/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\foxtr\LocalTools\excel-graft\corpus\templates\nested-groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{533C1DC2-1B7F-4B06-836F-907F2322682E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2453A8D9-6100-43F5-B02E-D5A0563A501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2470" windowWidth="28800" windowHeight="15910" xr2:uid="{12FD825E-9701-4788-9355-AF911BA81062}"/>
+    <workbookView xWindow="2240" yWindow="2470" windowWidth="28800" windowHeight="15910" xr2:uid="{828B528C-2D2B-40FE-A233-468DCAB70EC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" r:id="rId1"/>
@@ -338,21 +338,21 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>(Budget!$A$4,Budget!$A$9)</c:f>
+              <c:f>(Budget!$A$4,Budget!$A$10)</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>North</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>    Licenses</c:v>
+                  <c:v>South</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>(Budget!$B$4,Budget!$B$9)</c:f>
+              <c:f>(Budget!$B$4,Budget!$B$10)</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="2"/>
@@ -360,14 +360,14 @@
                   <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8000</c:v>
+                  <c:v>7700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-43F6-4D6C-887A-901329B299DA}"/>
+              <c16:uniqueId val="{00000000-0213-40E9-BE5C-3FC37D83E820}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -386,21 +386,21 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>(Budget!$A$4,Budget!$A$9)</c:f>
+              <c:f>(Budget!$A$4,Budget!$A$10)</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>North</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>    Licenses</c:v>
+                  <c:v>South</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>(Budget!$C$4,Budget!$C$9)</c:f>
+              <c:f>(Budget!$C$4,Budget!$C$10)</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="2"/>
@@ -408,14 +408,14 @@
                   <c:v>15150</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7600</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-43F6-4D6C-887A-901329B299DA}"/>
+              <c16:uniqueId val="{00000001-0213-40E9-BE5C-3FC37D83E820}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -429,11 +429,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1215296576"/>
-        <c:axId val="1886536495"/>
+        <c:axId val="1421733584"/>
+        <c:axId val="1267203887"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1215296576"/>
+        <c:axId val="1421733584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -476,7 +476,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1886536495"/>
+        <c:crossAx val="1267203887"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -484,7 +484,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1886536495"/>
+        <c:axId val="1267203887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -535,7 +535,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1215296576"/>
+        <c:crossAx val="1421733584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1154,7 +1154,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{081B92C2-331A-3E36-32D9-F51DC499CCE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9887F3E-9EB1-DCE3-ADD9-1C66176FA556}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1176,13 +1176,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E6C0C1A-68A0-4288-AE81-54863DB255EE}" name="Budget" displayName="Budget" ref="A3:D16" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="5">
-  <autoFilter ref="A3:D16" xr:uid="{0E6C0C1A-68A0-4288-AE81-54863DB255EE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88F94CE3-B690-4895-8D3A-2939892CF46F}" name="Budget" displayName="Budget" ref="A3:D16" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="5">
+  <autoFilter ref="A3:D16" xr:uid="{88F94CE3-B690-4895-8D3A-2939892CF46F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A38F8B5E-A4BB-4404-82A2-68F5BD18E95F}" name="Line"/>
-    <tableColumn id="2" xr3:uid="{AF59B09C-4136-4C50-8E97-D18876CB3F3C}" name="Budget" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{167BFF85-47E7-4616-93A4-DB6861901752}" name="Actual" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{C1C2C1DA-B6D5-420B-A089-DF7DDE222AD7}" name="Variance" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{38007CD5-77A3-44D0-8E0B-E4AF4ED1B533}" name="Line"/>
+    <tableColumn id="2" xr3:uid="{68734CBE-87BC-443B-8D5D-C26AFE378A6F}" name="Budget" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{C4226649-1B9A-43DF-9445-A21923D62CD9}" name="Actual" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{CE38B0A3-3E3B-4414-8BF3-8F251A6018DC}" name="Variance" dataDxfId="2">
       <calculatedColumnFormula>C4-B4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAADD98-B8C1-457B-BF75-772D14D69C40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{138EFF77-D6F0-4C0E-A090-AB996B8ED1B1}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
